--- a/combined_report.xlsx
+++ b/combined_report.xlsx
@@ -21,14 +21,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="$#,##0.000"/>
-    <numFmt numFmtId="168" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="169" formatCode="#,###0.000"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0_-;-* #,##0_-;_-* &quot; - &quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="#,###0.000"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0_-;-* #,##0_-;_-* &quot; - &quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -104,7 +103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -116,7 +115,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -128,7 +127,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/combined_report.xlsx
+++ b/combined_report.xlsx
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.34375</v>
+        <v>0.7090277777777778</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>normal hours</t>
+          <t>overtime 150%</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.7375</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>229.006</v>
+        <v>34.945</v>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>29.25</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>6698.426</v>
+        <v>1533.212</v>
       </c>
       <c r="M6" s="10" t="n"/>
     </row>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.7090277777777778</v>
+        <v>0.34375</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>overtime 150%</t>
+          <t>normal hours</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.7375</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>34.945</v>
+        <v>229.006</v>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>29.25</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>1533.212</v>
+        <v>6698.426</v>
       </c>
       <c r="M7" s="10" t="n"/>
     </row>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>overtime 150%</t>
+          <t>normal hours</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.6375</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>4.23</v>
+        <v>11.59</v>
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>18.25</v>
       </c>
       <c r="L8" s="15" t="n">
-        <v>115.796</v>
+        <v>211.517</v>
       </c>
       <c r="M8" s="10" t="n"/>
     </row>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.4861111111111111</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>normal hours</t>
+          <t>overtime 150%</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.6375</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>11.59</v>
+        <v>4.23</v>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>18.25</v>
       </c>
       <c r="L9" s="15" t="n">
-        <v>211.517</v>
+        <v>115.796</v>
       </c>
       <c r="M9" s="10" t="n"/>
     </row>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.7104166666666667</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>normal hours</t>
+          <t>overtime 150%</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.7069444444444445</v>
+        <v>0.7284722222222222</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>216.552</v>
+        <v>32.831</v>
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>29.25</v>
       </c>
       <c r="L10" s="15" t="n">
-        <v>6334.146</v>
+        <v>1440.46</v>
       </c>
       <c r="M10" s="10" t="n"/>
     </row>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.3409722222222222</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>overtime 150%</t>
+          <t>normal hours</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.7284722222222222</v>
+        <v>0.7069444444444445</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>32.831</v>
+        <v>216.552</v>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>29.25</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>1440.46</v>
+        <v>6334.146</v>
       </c>
       <c r="M11" s="10" t="n"/>
     </row>

--- a/combined_report.xlsx
+++ b/combined_report.xlsx
@@ -704,11 +704,11 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>0.3444444444444444</v>
+        <v>0.4736111111111111</v>
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>CCCS (CFTO)</t>
+          <t>Unload to Quay</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
@@ -722,21 +722,21 @@
         </is>
       </c>
       <c r="H2" s="11" t="n">
-        <v>0.7069444444444445</v>
+        <v>0.6652777777777777</v>
       </c>
       <c r="I2" s="13" t="n">
-        <v>118.033</v>
+        <v>26.25</v>
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>Unload to CCCS</t>
+          <t>Unload to Quay</t>
         </is>
       </c>
       <c r="K2" s="14" t="n">
-        <v>29.25</v>
+        <v>18.25</v>
       </c>
       <c r="L2" s="15" t="n">
-        <v>3452.465</v>
+        <v>479.063</v>
       </c>
       <c r="M2" s="10" t="n"/>
     </row>
@@ -755,11 +755,11 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>CCCS (CFTO)</t>
+          <t>Unload to Quay</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -773,21 +773,21 @@
         </is>
       </c>
       <c r="H3" s="11" t="n">
-        <v>0.7486111111111111</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="I3" s="13" t="n">
-        <v>31.548</v>
+        <v>8.73</v>
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>Unload to CCCS</t>
+          <t>Unload to Quay</t>
         </is>
       </c>
       <c r="K3" s="14" t="n">
-        <v>29.25</v>
+        <v>18.25</v>
       </c>
       <c r="L3" s="15" t="n">
-        <v>1384.169</v>
+        <v>238.984</v>
       </c>
       <c r="M3" s="10" t="n"/>
     </row>
@@ -806,11 +806,11 @@
         </is>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.4736111111111111</v>
+        <v>0.3444444444444444</v>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>Unload to Quay</t>
+          <t>CCCS (CFTO)</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -824,21 +824,21 @@
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.6652777777777777</v>
+        <v>0.7069444444444445</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>26.25</v>
+        <v>118.033</v>
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>Unload to Quay</t>
+          <t>Unload to CCCS</t>
         </is>
       </c>
       <c r="K4" s="14" t="n">
-        <v>18.25</v>
+        <v>29.25</v>
       </c>
       <c r="L4" s="15" t="n">
-        <v>479.063</v>
+        <v>3452.465</v>
       </c>
       <c r="M4" s="10" t="n"/>
     </row>
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Unload to Quay</t>
+          <t>CCCS (CFTO)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -875,21 +875,21 @@
         </is>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7486111111111111</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>8.73</v>
+        <v>31.548</v>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Unload to Quay</t>
+          <t>Unload to CCCS</t>
         </is>
       </c>
       <c r="K5" s="14" t="n">
-        <v>18.25</v>
+        <v>29.25</v>
       </c>
       <c r="L5" s="15" t="n">
-        <v>238.984</v>
+        <v>1384.169</v>
       </c>
       <c r="M5" s="10" t="n"/>
     </row>
@@ -908,11 +908,11 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.7090277777777778</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>CCCS (CFTO)</t>
+          <t>Unload to Quay</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.7375</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>34.945</v>
+        <v>4.23</v>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>Unload to CCCS</t>
+          <t>Unload to Quay</t>
         </is>
       </c>
       <c r="K6" s="14" t="n">
-        <v>29.25</v>
+        <v>18.25</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>1533.212</v>
+        <v>115.796</v>
       </c>
       <c r="M6" s="10" t="n"/>
     </row>
@@ -1061,11 +1061,11 @@
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7090277777777778</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Unload to Quay</t>
+          <t>CCCS (CFTO)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7375</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>4.23</v>
+        <v>34.945</v>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>Unload to Quay</t>
+          <t>Unload to CCCS</t>
         </is>
       </c>
       <c r="K9" s="14" t="n">
-        <v>18.25</v>
+        <v>29.25</v>
       </c>
       <c r="L9" s="15" t="n">
-        <v>115.796</v>
+        <v>1533.212</v>
       </c>
       <c r="M9" s="10" t="n"/>
     </row>
@@ -1112,16 +1112,16 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>CCCS (CFTO)</t>
+          <t>Unload to Quay</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>overtime 150%</t>
+          <t>normal hours</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.7284722222222222</v>
+        <v>0.5340277777777778</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>32.831</v>
+        <v>10.48</v>
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Unload to CCCS</t>
+          <t>Unload to Quay</t>
         </is>
       </c>
       <c r="K10" s="14" t="n">
-        <v>29.25</v>
+        <v>18.25</v>
       </c>
       <c r="L10" s="15" t="n">
-        <v>1440.46</v>
+        <v>191.26</v>
       </c>
       <c r="M10" s="10" t="n"/>
     </row>
@@ -1163,16 +1163,16 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.7340277777777777</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>CCCS (CFTO)</t>
+          <t>Unload to Quay</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>normal hours</t>
+          <t>overtime 150%</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.7069444444444445</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>216.552</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Unload to CCCS</t>
+          <t>Unload to Quay</t>
         </is>
       </c>
       <c r="K11" s="14" t="n">
-        <v>29.25</v>
+        <v>18.25</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>6334.146</v>
+        <v>235.972</v>
       </c>
       <c r="M11" s="10" t="n"/>
     </row>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.7104166666666667</v>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Unload to Quay</t>
+          <t>CCCS (CFTO)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>normal hours</t>
+          <t>overtime 150%</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -1232,21 +1232,21 @@
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.5340277777777778</v>
+        <v>0.7284722222222222</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>10.48</v>
+        <v>32.831</v>
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>Unload to Quay</t>
+          <t>Unload to CCCS</t>
         </is>
       </c>
       <c r="K12" s="14" t="n">
-        <v>18.25</v>
+        <v>29.25</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>191.26</v>
+        <v>1440.46</v>
       </c>
       <c r="M12" s="10" t="n"/>
     </row>
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.7340277777777777</v>
+        <v>0.3409722222222222</v>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Unload to Quay</t>
+          <t>CCCS (CFTO)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>overtime 150%</t>
+          <t>normal hours</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7069444444444445</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>8.619999999999999</v>
+        <v>216.552</v>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Unload to Quay</t>
+          <t>Unload to CCCS</t>
         </is>
       </c>
       <c r="K13" s="14" t="n">
-        <v>18.25</v>
+        <v>29.25</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>235.972</v>
+        <v>6334.146</v>
       </c>
       <c r="M13" s="10" t="n"/>
     </row>
